--- a/docs/downloads/04/tbl_schooling_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_schooling_alaotra_tous.xlsx
@@ -405,12 +405,6 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>3.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -441,12 +435,6 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>6.8</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -531,12 +519,6 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>5.6</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -602,12 +584,6 @@
         <is>
           <t>Non</t>
         </is>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>3</v>
       </c>
     </row>
     <row r="15">

--- a/docs/downloads/04/tbl_schooling_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_schooling_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -439,7 +439,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -457,7 +457,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">

--- a/docs/downloads/04/tbl_schooling_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_schooling_alaotra_tous.xlsx
@@ -421,7 +421,7 @@
         <v>55</v>
       </c>
       <c r="D4">
-        <v>96.5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>93.2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -469,7 +469,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>13.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -487,7 +487,7 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>86.8</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
@@ -535,7 +535,7 @@
         <v>68</v>
       </c>
       <c r="D11">
-        <v>94.40000000000001</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -553,7 +553,7 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -571,7 +571,7 @@
         <v>59</v>
       </c>
       <c r="D13">
-        <v>85.5</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
@@ -619,7 +619,7 @@
         <v>26</v>
       </c>
       <c r="D16">
-        <v>6.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -637,7 +637,7 @@
         <v>387</v>
       </c>
       <c r="D17">
-        <v>93.7</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
